--- a/artfynd/A 57026-2024 artfynd.xlsx
+++ b/artfynd/A 57026-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747373</v>
+        <v>122747369</v>
       </c>
       <c r="B2" t="n">
-        <v>78305</v>
+        <v>74802</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579318</v>
+        <v>579195</v>
       </c>
       <c r="R2" t="n">
-        <v>6516432</v>
+        <v>6516181</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På tallåga i kanten mot sumpskogen.</t>
+          <t>På senvuxen gran i sumpskog. 12 cm i brh. Bredvid torrträd av tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747367</v>
+        <v>122747373</v>
       </c>
       <c r="B3" t="n">
-        <v>74700</v>
+        <v>78407</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>N Oxmyran S, Srm</t>
+          <t>Kvinnfolksbaracken S, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579200</v>
+        <v>579318</v>
       </c>
       <c r="R3" t="n">
-        <v>6516171</v>
+        <v>6516432</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Kattfotslav på gran i sumpskog. 18 cm i brh.</t>
+          <t>På tallåga i kanten mot sumpskogen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747369</v>
+        <v>122747367</v>
       </c>
       <c r="B4" t="n">
-        <v>74700</v>
+        <v>74802</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,14 +933,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvinnfolksbaracken S, Srm</t>
+          <t>N Oxmyran S, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579195</v>
+        <v>579200</v>
       </c>
       <c r="R4" t="n">
-        <v>6516181</v>
+        <v>6516171</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På senvuxen gran i sumpskog. 12 cm i brh. Bredvid torrträd av tall.</t>
+          <t>Kattfotslav på gran i sumpskog. 18 cm i brh.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 57026-2024 artfynd.xlsx
+++ b/artfynd/A 57026-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>122747373</v>
       </c>
       <c r="B3" t="n">
-        <v>78407</v>
+        <v>78411</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57026-2024 artfynd.xlsx
+++ b/artfynd/A 57026-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747369</v>
+        <v>122747373</v>
       </c>
       <c r="B2" t="n">
-        <v>74802</v>
+        <v>78411</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579195</v>
+        <v>579318</v>
       </c>
       <c r="R2" t="n">
-        <v>6516181</v>
+        <v>6516432</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På senvuxen gran i sumpskog. 12 cm i brh. Bredvid torrträd av tall.</t>
+          <t>På tallåga i kanten mot sumpskogen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747373</v>
+        <v>122747369</v>
       </c>
       <c r="B3" t="n">
-        <v>78411</v>
+        <v>74802</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579318</v>
+        <v>579195</v>
       </c>
       <c r="R3" t="n">
-        <v>6516432</v>
+        <v>6516181</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På tallåga i kanten mot sumpskogen.</t>
+          <t>På senvuxen gran i sumpskog. 12 cm i brh. Bredvid torrträd av tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 57026-2024 artfynd.xlsx
+++ b/artfynd/A 57026-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Helene Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 57026-2024 artfynd.xlsx
+++ b/artfynd/A 57026-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747373</v>
+        <v>122747369</v>
       </c>
       <c r="B2" t="n">
-        <v>78411</v>
+        <v>74802</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579318</v>
+        <v>579195</v>
       </c>
       <c r="R2" t="n">
-        <v>6516432</v>
+        <v>6516181</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På tallåga i kanten mot sumpskogen.</t>
+          <t>På senvuxen gran i sumpskog. 12 cm i brh. Bredvid torrträd av tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747369</v>
+        <v>122747367</v>
       </c>
       <c r="B3" t="n">
         <v>74802</v>
@@ -822,14 +822,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvinnfolksbaracken S, Srm</t>
+          <t>N Oxmyran S, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579195</v>
+        <v>579200</v>
       </c>
       <c r="R3" t="n">
-        <v>6516181</v>
+        <v>6516171</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På senvuxen gran i sumpskog. 12 cm i brh. Bredvid torrträd av tall.</t>
+          <t>Kattfotslav på gran i sumpskog. 18 cm i brh.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747367</v>
+        <v>122747373</v>
       </c>
       <c r="B4" t="n">
-        <v>74802</v>
+        <v>78411</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>N Oxmyran S, Srm</t>
+          <t>Kvinnfolksbaracken S, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579200</v>
+        <v>579318</v>
       </c>
       <c r="R4" t="n">
-        <v>6516171</v>
+        <v>6516432</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kattfotslav på gran i sumpskog. 18 cm i brh.</t>
+          <t>På tallåga i kanten mot sumpskogen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Helene Andersson, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 57026-2024 artfynd.xlsx
+++ b/artfynd/A 57026-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747369</v>
+        <v>122747367</v>
       </c>
       <c r="B2" t="n">
         <v>74802</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvinnfolksbaracken S, Srm</t>
+          <t>N Oxmyran S, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579195</v>
+        <v>579200</v>
       </c>
       <c r="R2" t="n">
-        <v>6516181</v>
+        <v>6516171</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På senvuxen gran i sumpskog. 12 cm i brh. Bredvid torrträd av tall.</t>
+          <t>Kattfotslav på gran i sumpskog. 18 cm i brh.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747367</v>
+        <v>122747369</v>
       </c>
       <c r="B3" t="n">
         <v>74802</v>
@@ -822,14 +822,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>N Oxmyran S, Srm</t>
+          <t>Kvinnfolksbaracken S, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579200</v>
+        <v>579195</v>
       </c>
       <c r="R3" t="n">
-        <v>6516171</v>
+        <v>6516181</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Kattfotslav på gran i sumpskog. 18 cm i brh.</t>
+          <t>På senvuxen gran i sumpskog. 12 cm i brh. Bredvid torrträd av tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 57026-2024 artfynd.xlsx
+++ b/artfynd/A 57026-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747367</v>
+        <v>122747373</v>
       </c>
       <c r="B2" t="n">
-        <v>74802</v>
+        <v>78411</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N Oxmyran S, Srm</t>
+          <t>Kvinnfolksbaracken S, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579200</v>
+        <v>579318</v>
       </c>
       <c r="R2" t="n">
-        <v>6516171</v>
+        <v>6516432</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Kattfotslav på gran i sumpskog. 18 cm i brh.</t>
+          <t>På tallåga i kanten mot sumpskogen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747373</v>
+        <v>122747367</v>
       </c>
       <c r="B4" t="n">
-        <v>78411</v>
+        <v>74802</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvinnfolksbaracken S, Srm</t>
+          <t>N Oxmyran S, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579318</v>
+        <v>579200</v>
       </c>
       <c r="R4" t="n">
-        <v>6516432</v>
+        <v>6516171</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På tallåga i kanten mot sumpskogen.</t>
+          <t>Kattfotslav på gran i sumpskog. 18 cm i brh.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 57026-2024 artfynd.xlsx
+++ b/artfynd/A 57026-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747373</v>
+        <v>122747367</v>
       </c>
       <c r="B2" t="n">
-        <v>78411</v>
+        <v>74802</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvinnfolksbaracken S, Srm</t>
+          <t>N Oxmyran S, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579318</v>
+        <v>579200</v>
       </c>
       <c r="R2" t="n">
-        <v>6516432</v>
+        <v>6516171</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På tallåga i kanten mot sumpskogen.</t>
+          <t>Kattfotslav på gran i sumpskog. 18 cm i brh.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747369</v>
+        <v>122747373</v>
       </c>
       <c r="B3" t="n">
-        <v>74802</v>
+        <v>78411</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579195</v>
+        <v>579318</v>
       </c>
       <c r="R3" t="n">
-        <v>6516181</v>
+        <v>6516432</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På senvuxen gran i sumpskog. 12 cm i brh. Bredvid torrträd av tall.</t>
+          <t>På tallåga i kanten mot sumpskogen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747367</v>
+        <v>122747369</v>
       </c>
       <c r="B4" t="n">
         <v>74802</v>
@@ -933,14 +933,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>N Oxmyran S, Srm</t>
+          <t>Kvinnfolksbaracken S, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579200</v>
+        <v>579195</v>
       </c>
       <c r="R4" t="n">
-        <v>6516171</v>
+        <v>6516181</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kattfotslav på gran i sumpskog. 18 cm i brh.</t>
+          <t>På senvuxen gran i sumpskog. 12 cm i brh. Bredvid torrträd av tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 57026-2024 artfynd.xlsx
+++ b/artfynd/A 57026-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747367</v>
+        <v>122747373</v>
       </c>
       <c r="B2" t="n">
-        <v>74802</v>
+        <v>78411</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N Oxmyran S, Srm</t>
+          <t>Kvinnfolksbaracken S, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579200</v>
+        <v>579318</v>
       </c>
       <c r="R2" t="n">
-        <v>6516171</v>
+        <v>6516432</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Kattfotslav på gran i sumpskog. 18 cm i brh.</t>
+          <t>På tallåga i kanten mot sumpskogen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747373</v>
+        <v>122747369</v>
       </c>
       <c r="B3" t="n">
-        <v>78411</v>
+        <v>74802</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579318</v>
+        <v>579195</v>
       </c>
       <c r="R3" t="n">
-        <v>6516432</v>
+        <v>6516181</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På tallåga i kanten mot sumpskogen.</t>
+          <t>På senvuxen gran i sumpskog. 12 cm i brh. Bredvid torrträd av tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747369</v>
+        <v>122747367</v>
       </c>
       <c r="B4" t="n">
         <v>74802</v>
@@ -933,14 +933,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvinnfolksbaracken S, Srm</t>
+          <t>N Oxmyran S, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579195</v>
+        <v>579200</v>
       </c>
       <c r="R4" t="n">
-        <v>6516181</v>
+        <v>6516171</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På senvuxen gran i sumpskog. 12 cm i brh. Bredvid torrträd av tall.</t>
+          <t>Kattfotslav på gran i sumpskog. 18 cm i brh.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 57026-2024 artfynd.xlsx
+++ b/artfynd/A 57026-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747373</v>
+        <v>122747367</v>
       </c>
       <c r="B2" t="n">
-        <v>78411</v>
+        <v>74805</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvinnfolksbaracken S, Srm</t>
+          <t>N Oxmyran S, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579318</v>
+        <v>579200</v>
       </c>
       <c r="R2" t="n">
-        <v>6516432</v>
+        <v>6516171</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På tallåga i kanten mot sumpskogen.</t>
+          <t>Kattfotslav på gran i sumpskog. 18 cm i brh.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747369</v>
+        <v>122747373</v>
       </c>
       <c r="B3" t="n">
-        <v>74802</v>
+        <v>78414</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579195</v>
+        <v>579318</v>
       </c>
       <c r="R3" t="n">
-        <v>6516181</v>
+        <v>6516432</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På senvuxen gran i sumpskog. 12 cm i brh. Bredvid torrträd av tall.</t>
+          <t>På tallåga i kanten mot sumpskogen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747367</v>
+        <v>122747369</v>
       </c>
       <c r="B4" t="n">
-        <v>74802</v>
+        <v>74805</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,14 +933,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>N Oxmyran S, Srm</t>
+          <t>Kvinnfolksbaracken S, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579200</v>
+        <v>579195</v>
       </c>
       <c r="R4" t="n">
-        <v>6516171</v>
+        <v>6516181</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kattfotslav på gran i sumpskog. 18 cm i brh.</t>
+          <t>På senvuxen gran i sumpskog. 12 cm i brh. Bredvid torrträd av tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 57026-2024 artfynd.xlsx
+++ b/artfynd/A 57026-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747367</v>
+        <v>122747373</v>
       </c>
       <c r="B2" t="n">
-        <v>74805</v>
+        <v>78416</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N Oxmyran S, Srm</t>
+          <t>Kvinnfolksbaracken S, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579200</v>
+        <v>579318</v>
       </c>
       <c r="R2" t="n">
-        <v>6516171</v>
+        <v>6516432</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Kattfotslav på gran i sumpskog. 18 cm i brh.</t>
+          <t>På tallåga i kanten mot sumpskogen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747373</v>
+        <v>122747369</v>
       </c>
       <c r="B3" t="n">
-        <v>78414</v>
+        <v>74805</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579318</v>
+        <v>579195</v>
       </c>
       <c r="R3" t="n">
-        <v>6516432</v>
+        <v>6516181</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På tallåga i kanten mot sumpskogen.</t>
+          <t>På senvuxen gran i sumpskog. 12 cm i brh. Bredvid torrträd av tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747369</v>
+        <v>122747367</v>
       </c>
       <c r="B4" t="n">
         <v>74805</v>
@@ -933,14 +933,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvinnfolksbaracken S, Srm</t>
+          <t>N Oxmyran S, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579195</v>
+        <v>579200</v>
       </c>
       <c r="R4" t="n">
-        <v>6516181</v>
+        <v>6516171</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På senvuxen gran i sumpskog. 12 cm i brh. Bredvid torrträd av tall.</t>
+          <t>Kattfotslav på gran i sumpskog. 18 cm i brh.</t>
         </is>
       </c>
       <c r="AD4" t="b">
